--- a/data/output/2025/evaluasi_32.xlsx
+++ b/data/output/2025/evaluasi_32.xlsx
@@ -33,6 +33,8 @@
     <sheet name="3273" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="3274" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="3275" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="3201" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="3216" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1364,7 +1366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,6 +1482,146 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>38.91053590824374</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.363630583497689</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.098805031901266</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5315239645011242</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.962275777722882</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,6 +1780,90 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukabumi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>33.8485</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukabumi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.53175949299904</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukabumi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9.526179392507702</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2020,6 +2246,146 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3217</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung Barat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>21.83188240136068</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3217</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung Barat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.57596267063089</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3217</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung Barat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6133102182601786</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3217</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung Barat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.35088739876333</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3217</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung Barat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2458668226151408</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,6 +2600,62 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3213</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Subang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>80.64680995608937</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3213</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Subang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.654106940906329</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2616,6 +3038,118 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-3 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>48.28774498549511</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.65858842936472</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.72846388951677</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.05571287926990924</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2630,7 +3164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2746,6 +3280,258 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>23.76213804258841</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.733970168168387</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.397284724915551</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8.586597681643159</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.681534405308382</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.30283500900135</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.6467290855338951</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.641484995529759</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-5.499548074983627</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2760,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2820,6 +3606,90 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>24.32519999310636</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.861000212738678</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.25552127274447</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2834,7 +3704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2922,6 +3792,90 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3207</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Ciamis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.81000805986417</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3207</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Ciamis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.759679079001796</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3207</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Ciamis</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.687536235066332</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2936,7 +3890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2996,6 +3950,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>25.33158942347199</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.33224220925253</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3010,7 +4020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3070,6 +4080,90 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>21.11984558269958</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.501780885389886</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.133261244669937</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3382,7 +4476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3442,6 +4536,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3210</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Majalengka</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20.35682190016289</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3210</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Majalengka</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.674127349332569</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3210</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Majalengka</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.5444098994416</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3210</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Majalengka</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.612781590593968</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3456,7 +4662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3544,6 +4750,62 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3211</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumedang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>48.22304763407882</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3211</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumedang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.02277357620421</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3558,7 +4820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3618,6 +4880,62 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Indramayu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>38.74974123588002</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Indramayu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.08773104791963</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3632,7 +4950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3692,6 +5010,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangandaran</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.521088374691459</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3706,7 +5052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3766,6 +5112,174 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3273</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bandung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.208223099331944</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3273</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bandung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>35.40874195522311</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3273</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bandung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5329291897160182</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3273</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Bandung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.251902107130179</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3273</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Bandung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.263329266056038</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3273</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Bandung</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6.649265763764199</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3780,7 +5294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4008,6 +5522,202 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>67.70834068476191</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.03540728993835</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-7.652174242453019</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.144276793992116</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.7097275649994</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.9995814633502772</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.8358903375088149</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4022,7 +5732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4082,6 +5792,574 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3275</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>62.93164884674464</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3275</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.442123568027199</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3275</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.87904291916032</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.7960696736689763</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.125812430021282</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17.35893944136296</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-6.302158584535198</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8067217810947171</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.54381935525661</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5568558851306723</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-12.9159453706405</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-3.896971723909195</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-5.8199794119988</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.270103466994021</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bekasi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>20.38032731309949</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bekasi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.619194940009435</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bekasi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.156849237385235</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4096,7 +6374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4450,18 +6728,270 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>9.984381447670962</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.260000000000001</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>78.009</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>9.785650430815759</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-3.253665023817038</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.015946883048671</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.78314440284144</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-5.961280997651065</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-1.769050225297559</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>2.113339805970704</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4478,7 +7008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4566,6 +7096,90 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>23.89542402786412</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.610387278045788</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.80068776884072</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4580,7 +7194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4864,6 +7478,202 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-6.947165558378024</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>43.42691937995905</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.631159758141125</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>26.02810816968256</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.761688858119105</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1568461270257747</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4.945954811321599</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4878,7 +7688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5134,6 +7944,62 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9.965047912293933</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-3.222972184839923</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5278,7 +8144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5394,6 +8260,34 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3276</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Depok</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>48.07342811511995</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5408,7 +8302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5499,6 +8393,230 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.782464198042963</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>62.9049467932861</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.435472371131384</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.06307559412687216</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3630963797048177</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.4532395170787075</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8.975809979601513</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.63251039178174</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
